--- a/artfynd/A 63444-2025 artfynd.xlsx
+++ b/artfynd/A 63444-2025 artfynd.xlsx
@@ -675,53 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90907262</v>
+        <v>112168736</v>
       </c>
       <c r="B2" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Duorbunoajvve, Lu lm</t>
+          <t>Tuorponåive, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691496.9444188941</v>
+        <v>691560</v>
       </c>
       <c r="R2" t="n">
-        <v>7414187.960357067</v>
+        <v>7414190</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-09-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-09-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,83 +757,67 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Beren van Duijn</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Charles Campbell</t>
+          <t>Magnus Enbom</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Charles Campbell</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Statens Fastighetsverk - NVB - Greensway</t>
-        </is>
-      </c>
+          <t>Magnus Enbom</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112168736</v>
+        <v>90907262</v>
       </c>
       <c r="B3" t="n">
-        <v>90152</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tuorponåive, Lu lm</t>
+          <t>Duorbunoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691560</v>
+        <v>691497</v>
       </c>
       <c r="R3" t="n">
-        <v>7414190</v>
+        <v>7414188</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2019-09-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2019-09-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,34 +855,37 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Beren van Duijn</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Enbom</t>
+          <t>Charles Campbell</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Enbom</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Via Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Statens Fastighetsverk - NVB - Greensway</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>112168726</v>
       </c>
       <c r="B4" t="n">
-        <v>5436</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5495</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,7 +922,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691609</v>
+        <v>691610</v>
       </c>
       <c r="R4" t="n">
         <v>7414239</v>

--- a/artfynd/A 63444-2025 artfynd.xlsx
+++ b/artfynd/A 63444-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112168736</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -877,6 +887,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Statens Fastighetsverk - NVB - Greensway</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90907262</t>
         </is>
       </c>
     </row>
@@ -982,8 +997,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112168726</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>